--- a/public/static/产品工序单价导入模板.xlsx
+++ b/public/static/产品工序单价导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="30720" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="产品工序单价" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>序号</t>
   </si>
@@ -84,6 +84,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>计价类型(</t>
     </r>
     <r>
@@ -109,7 +116,39 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>单价(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>生效日期(</t>
     </r>
     <r>
       <rPr>
@@ -136,24 +175,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>计件</t>
+    <t>不计工资</t>
   </si>
   <si>
     <t>说明：</t>
   </si>
   <si>
-    <t>1、计价类型：计件、计时</t>
+    <t>1、计价类型：计件、计时、不计工资</t>
+  </si>
+  <si>
+    <t>2、生效日期(必填)格式：yyyy-MM-dd 示例：2024-9-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -832,7 +875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -855,6 +898,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1390,17 +1436,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.44444444444444" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="22.2222222222222" customWidth="1"/>
     <col min="4" max="4" width="17.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="17.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:5">
+    <row r="1" ht="25" customHeight="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1416,19 +1463,28 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:5">
+    <row r="2" ht="20" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"计件,计时,不计工资"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1437,20 +1493,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="82.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="101.333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
